--- a/Packages/cn.etetet.startconfig/Luban/Release/Datas/StartScene.xlsx
+++ b/Packages/cn.etetet.startconfig/Luban/Release/Datas/StartScene.xlsx
@@ -15,7 +15,7 @@
   <sheets>
     <sheet name="StartSceneConfig" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" fullCalcOnLoad="1" fullPrecision="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>##var</t>
   </si>
@@ -82,6 +82,9 @@
     <t>外网端口</t>
   </si>
   <si>
+    <t>ServiceDiscovery</t>
+  </si>
+  <si>
     <t>RouterManager</t>
   </si>
   <si>
@@ -98,25 +101,20 @@
   </si>
   <si>
     <t>MapManager</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>ServiceDiscovery</t>
+    <t/>
   </si>
   <si>
-    <t>Router</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Gate</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <t>Match</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <numFmts count="0"/>
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -154,13 +152,6 @@
       <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -200,32 +191,32 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" applyNumberFormat="0" fontId="2" applyFont="1" fillId="3" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" applyNumberFormat="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="0" xfId="2" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="3" applyFill="1" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" applyFont="1" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" applyFont="1" fillId="4" applyFill="1" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="差" xfId="2" builtinId="27"/>
+    <cellStyle name="差" xfId="1" builtinId="27"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="好" xfId="1" builtinId="26"/>
+    <cellStyle name="好" xfId="2" builtinId="26"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -527,19 +518,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CTZ10"/>
+  <dimension ref="A1:CTZ11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="21.1640625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="12.6640625" style="3" customWidth="1"/>
-    <col min="3" max="4" width="12.6640625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="14.6640625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="13.33203125" style="4" customWidth="1"/>
-    <col min="7" max="7" width="13.1640625" style="4" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="3"/>
+    <col min="1" max="1" width="21.1640625" customWidth="1" style="3"/>
+    <col min="2" max="2" width="12.6640625" customWidth="1" style="3"/>
+    <col min="3" max="4" width="12.6640625" customWidth="1" style="4"/>
+    <col min="5" max="5" width="14.6640625" customWidth="1" style="4"/>
+    <col min="6" max="6" width="13.33203125" customWidth="1" style="4"/>
+    <col min="7" max="7" width="13.1640625" customWidth="1" style="4"/>
+    <col min="8" max="16384" width="9" customWidth="1" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2574" s="1" customFormat="1" ht="15">
+    <row r="1" ht="15" s="1" customFormat="1">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -3129,7 +3120,7 @@
       <c r="CTY1" s="4"/>
       <c r="CTZ1" s="4"/>
     </row>
-    <row r="2" spans="1:2574" s="2" customFormat="1" ht="15">
+    <row r="2" ht="15" s="2" customFormat="1">
       <c r="A2" s="4" t="s">
         <v>7</v>
       </c>
@@ -5719,7 +5710,7 @@
       <c r="CTY2" s="4"/>
       <c r="CTZ2" s="4"/>
     </row>
-    <row r="3" spans="1:2574" s="1" customFormat="1" ht="15">
+    <row r="3" ht="15" s="1" customFormat="1">
       <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
@@ -8309,7 +8300,7 @@
       <c r="CTY3" s="4"/>
       <c r="CTZ3" s="4"/>
     </row>
-    <row r="4" spans="1:2574" customFormat="1">
+    <row r="4">
       <c r="B4" s="6">
         <v>1</v>
       </c>
@@ -8319,14 +8310,14 @@
       <c r="D4" s="6">
         <v>1</v>
       </c>
-      <c r="E4" t="s">
-        <v>22</v>
+      <c r="E4" s="0" t="s">
+        <v>16</v>
       </c>
-      <c r="F4" t="s">
-        <v>22</v>
+      <c r="F4" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:2574">
+    <row r="5">
       <c r="B5" s="6">
         <v>2</v>
       </c>
@@ -8337,16 +8328,16 @@
         <v>1</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G5" s="6">
         <v>10101</v>
       </c>
     </row>
-    <row r="6" spans="1:2574">
+    <row r="6">
       <c r="B6" s="6">
         <v>3</v>
       </c>
@@ -8357,14 +8348,14 @@
         <v>1</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G6" s="6"/>
     </row>
-    <row r="7" spans="1:2574" ht="15">
+    <row r="7" ht="15">
       <c r="B7" s="6">
         <v>14</v>
       </c>
@@ -8374,15 +8365,15 @@
       <c r="D7" s="6">
         <v>1</v>
       </c>
-      <c r="E7" t="s">
-        <v>18</v>
+      <c r="E7" s="0" t="s">
+        <v>19</v>
       </c>
-      <c r="F7" t="s">
-        <v>18</v>
+      <c r="F7" s="0" t="s">
+        <v>19</v>
       </c>
       <c r="G7" s="6"/>
     </row>
-    <row r="8" spans="1:2574">
+    <row r="8">
       <c r="B8" s="6">
         <v>15</v>
       </c>
@@ -8393,14 +8384,14 @@
         <v>1</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G8" s="6"/>
     </row>
-    <row r="9" spans="1:2574" ht="15">
+    <row r="9" ht="15">
       <c r="A9"/>
       <c r="B9" s="6">
         <v>25</v>
@@ -8412,14 +8403,14 @@
         <v>1</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G9" s="6"/>
     </row>
-    <row r="10" spans="1:2574" ht="15">
+    <row r="10" ht="15">
       <c r="A10"/>
       <c r="B10" s="6">
         <v>26</v>
@@ -8431,16 +8422,44 @@
         <v>1</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
-      <c r="G10" s="6"/>
+      <c r="G10" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="3">
+        <v>27</v>
+      </c>
+      <c r="C11" s="4">
+        <v>27</v>
+      </c>
+      <c r="D11" s="4">
+        <v>1</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>23</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
+</file>
+
+<file path=EPPlusLicense.txt>This workbook was created with the EPPlus library, licensed to ETET under the Polyform Noncommercial license, see https://polyformproject.org/licenses/noncommercial/1.0.0
+For more information about EPPlus, see https://epplussoftware.com/
+
 </file>